--- a/e2e-automationFaseIII/Vaciados/casos_prueba.xlsx
+++ b/e2e-automationFaseIII/Vaciados/casos_prueba.xlsx
@@ -47,7 +47,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -78,6 +78,12 @@
         <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -106,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -123,6 +129,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -672,9 +681,9 @@
       <c r="U2" s="2" t="n"/>
       <c r="V2" s="2" t="n"/>
       <c r="W2" s="2" t="n"/>
-      <c r="X2" s="7" t="inlineStr">
-        <is>
-          <t>OK (CRUD/Create)</t>
+      <c r="X2" s="8" t="inlineStr">
+        <is>
+          <t>ERROR: Notificaciones</t>
         </is>
       </c>
     </row>
@@ -719,7 +728,7 @@
       <c r="W3" s="2" t="n"/>
       <c r="X3" s="7" t="inlineStr">
         <is>
-          <t>OK (CRUD/Read - stub)</t>
+          <t>ENCONTRADO: 1 fila(s) (Código=X) → codigo=X | idioma=es-CL | descripcion=prueba QA</t>
         </is>
       </c>
     </row>

--- a/e2e-automationFaseIII/Vaciados/casos_prueba.xlsx
+++ b/e2e-automationFaseIII/Vaciados/casos_prueba.xlsx
@@ -681,9 +681,9 @@
       <c r="U2" s="2" t="n"/>
       <c r="V2" s="2" t="n"/>
       <c r="W2" s="2" t="n"/>
-      <c r="X2" s="8" t="inlineStr">
-        <is>
-          <t>ERROR: Notificaciones</t>
+      <c r="X2" s="7" t="inlineStr">
+        <is>
+          <t>OK (CRUD/Create)</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       <c r="W3" s="2" t="n"/>
       <c r="X3" s="7" t="inlineStr">
         <is>
-          <t>ENCONTRADO: 1 fila(s) (Código=X) → codigo=X | idioma=es-CL | descripcion=prueba QA</t>
+          <t>ENCONTRADO: 1 fila(s) (Código=X) → codigo=X | idioma=es-CL | descripcion=CREA QA AUT May 26</t>
         </is>
       </c>
     </row>

--- a/e2e-automationFaseIII/Vaciados/casos_prueba.xlsx
+++ b/e2e-automationFaseIII/Vaciados/casos_prueba.xlsx
@@ -47,7 +47,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -74,14 +74,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
         <bgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -112,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -132,6 +138,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -499,13 +508,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X4"/>
+  <dimension ref="A1:X5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" outlineLevelCol="0"/>
   <cols>
     <col width="73.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="11.88671875" bestFit="1" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="8.21875" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="22.21875" bestFit="1" customWidth="1" min="4" max="4"/>
     <col width="11.6640625" bestFit="1" customWidth="1" min="5" max="5"/>
     <col width="33.6640625" bestFit="1" customWidth="1" min="6" max="6"/>
     <col width="28" customWidth="1" min="7" max="23"/>
@@ -681,9 +690,9 @@
       <c r="U2" s="2" t="n"/>
       <c r="V2" s="2" t="n"/>
       <c r="W2" s="2" t="n"/>
-      <c r="X2" s="7" t="inlineStr">
-        <is>
-          <t>OK (CRUD/Create)</t>
+      <c r="X2" s="8" t="inlineStr">
+        <is>
+          <t>FALLO: no se encontró el botón '+ Añadir'</t>
         </is>
       </c>
     </row>
@@ -726,16 +735,16 @@
       <c r="U3" s="2" t="n"/>
       <c r="V3" s="2" t="n"/>
       <c r="W3" s="2" t="n"/>
-      <c r="X3" s="7" t="inlineStr">
-        <is>
-          <t>ENCONTRADO: 1 fila(s) (Código=X) → codigo=X | idioma=es-CL | descripcion=CREA QA AUT May 26</t>
+      <c r="X3" s="8" t="inlineStr">
+        <is>
+          <t>NO ENCONTRADO (Código=X)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Participes LATAM &gt; Maestros &gt; Configuración &gt; Varias &gt; Grupos Actividades Economicas</t>
+          <t>Maestros &gt; Básicos &gt; Nombres tarifas</t>
         </is>
       </c>
       <c r="B4" s="3">
@@ -744,20 +753,16 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Update</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Código.X</t>
+          <t>Create</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Nombre.Nombre Tarif QA</t>
         </is>
       </c>
       <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Descripción.CREA QA AUT May 26 MOD</t>
-        </is>
-      </c>
+      <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="n"/>
       <c r="H4" s="2" t="n"/>
       <c r="I4" s="2" t="n"/>
@@ -775,21 +780,66 @@
       <c r="U4" s="2" t="n"/>
       <c r="V4" s="2" t="n"/>
       <c r="W4" s="2" t="n"/>
-      <c r="X4" s="7" t="inlineStr">
-        <is>
-          <t>OK (CRUD/Update - stub)</t>
+      <c r="X4" s="9" t="inlineStr">
+        <is>
+          <t>OK (CRUD/Create)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Maestros &gt; Básicos &gt; Nombres tarifas</t>
+        </is>
+      </c>
+      <c r="B5" s="3">
+        <f>VLOOKUP(A5,'OpcionesThunder 2.5'!$B$2:$C$362,2,FALSE)</f>
+        <v/>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Nombre.Nombre Tarif QA</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
+      <c r="J5" s="2" t="n"/>
+      <c r="K5" s="2" t="n"/>
+      <c r="L5" s="2" t="n"/>
+      <c r="M5" s="2" t="n"/>
+      <c r="N5" s="2" t="n"/>
+      <c r="O5" s="2" t="n"/>
+      <c r="P5" s="2" t="n"/>
+      <c r="Q5" s="2" t="n"/>
+      <c r="R5" s="2" t="n"/>
+      <c r="S5" s="2" t="n"/>
+      <c r="T5" s="2" t="n"/>
+      <c r="U5" s="2" t="n"/>
+      <c r="V5" s="2" t="n"/>
+      <c r="W5" s="2" t="n"/>
+      <c r="X5" s="9" t="inlineStr">
+        <is>
+          <t>ENCONTRADO: 1 fila(s) (Nombre=Nombre Tarif QA) → codigo=807 | nombre=Nombre Tarif QA</t>
         </is>
       </c>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation sqref="B5:B997" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Tipo no válido" error="Selecciona: Consulta, CRUD o Transacciones" type="list">
+    <dataValidation sqref="B6:B996" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Tipo no válido" error="Selecciona: Consulta, CRUD o Transacciones" type="list">
       <formula1>"Consulta,CRUD,Transacciones"</formula1>
     </dataValidation>
-    <dataValidation sqref="B2:B4" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Tipo no válido" error="Selecciona uno: Consulta, CRUD o Transacciones" promptTitle="Tipo de pantalla" prompt="Elige el tipo: Consulta, CRUD o Transacciones" type="list">
+    <dataValidation sqref="B2:B5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Tipo no válido" error="Selecciona uno: Consulta, CRUD o Transacciones" promptTitle="Tipo de pantalla" prompt="Elige el tipo: Consulta, CRUD o Transacciones" type="list">
       <formula1>"Consulta,CRUD,Transacciones"</formula1>
     </dataValidation>
-    <dataValidation sqref="C2:C997" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Acción no válida" error="Selecciona: Create, Read, Update o Delete (vacío para Consulta)" type="list">
+    <dataValidation sqref="C2:C996" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Acción no válida" error="Selecciona: Create, Read, Update o Delete (vacío para Consulta)" type="list">
       <formula1>"Create,Read,Update,Delete"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2051,7 +2101,7 @@
         </is>
       </c>
     </row>
-    <row r="84">
+    <row r="84" hidden="1">
       <c r="A84" t="n">
         <v>83</v>
       </c>
@@ -2146,7 +2196,7 @@
         </is>
       </c>
     </row>
-    <row r="90">
+    <row r="90" hidden="1">
       <c r="A90" t="n">
         <v>89</v>
       </c>
@@ -2506,7 +2556,7 @@
         </is>
       </c>
     </row>
-    <row r="114">
+    <row r="114" hidden="1">
       <c r="A114" t="n">
         <v>113</v>
       </c>
@@ -3079,7 +3129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154">
+    <row r="154" hidden="1">
       <c r="A154" t="n">
         <v>153</v>
       </c>
@@ -3092,7 +3142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155">
+    <row r="155" hidden="1">
       <c r="A155" t="n">
         <v>154</v>
       </c>
@@ -3105,7 +3155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156">
+    <row r="156" hidden="1">
       <c r="A156" t="n">
         <v>155</v>
       </c>
@@ -3444,7 +3494,7 @@
         </is>
       </c>
     </row>
-    <row r="179" hidden="1">
+    <row r="179">
       <c r="A179" t="n">
         <v>178</v>
       </c>
@@ -5154,7 +5204,7 @@
         </is>
       </c>
     </row>
-    <row r="291">
+    <row r="291" hidden="1">
       <c r="A291" t="n">
         <v>290</v>
       </c>
@@ -6253,13 +6303,7 @@
   <autoFilter ref="A1:D362">
     <filterColumn colId="1" hiddenButton="0" showButton="1">
       <filters>
-        <filter val="Maestros &gt; Entidades &gt; Básicos &gt; Actividades Económicas"/>
-        <filter val="Participes LATAM &gt; Maestros &gt; Configuración &gt; Varias &gt; Actividades Económicas"/>
-        <filter val="Participes LATAM &gt; Maestros &gt; Configuración &gt; Varias &gt; Grupos Actividades Economicas"/>
-        <filter val="Participes LATAM &gt; Maestros &gt; Participes &gt; Mantenimientos &gt; Actividades Económicas"/>
-        <filter val="Participes LATAM &gt; Procesos &gt; Operaciones &gt; Actividades Económicas"/>
-        <filter val="Participes LATAM &gt; Procesos &gt; Operaciones &gt; Cesiones de Cuotas &gt; Actividades Económicas"/>
-        <filter val="Participes LATAM &gt; Procesos &gt; Utilidades/Subprocesos &gt; Actividades Económicas"/>
+        <filter val="Maestros &gt; Básicos &gt; Nombres tarifas"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -6602,7 +6646,7 @@
   <dimension ref="A1:X5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="28.8" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Camino a la Pantalla</t>
@@ -6724,7 +6768,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="43.2" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
           <t>Participes LATAM &gt; Maestros &gt; Configuración &gt; Varias &gt; Grupos Actividades Economicas</t>
@@ -6814,7 +6858,7 @@
       <c r="W3" s="2" t="n"/>
       <c r="X3" s="2" t="n"/>
     </row>
-    <row r="4">
+    <row r="4" ht="57.6" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
           <t>Participes LATAM &gt; Maestros &gt; Configuración &gt; Varias &gt; Grupos Actividades Economicas</t>

--- a/e2e-automationFaseIII/Vaciados/casos_prueba.xlsx
+++ b/e2e-automationFaseIII/Vaciados/casos_prueba.xlsx
@@ -690,9 +690,9 @@
       <c r="U2" s="2" t="n"/>
       <c r="V2" s="2" t="n"/>
       <c r="W2" s="2" t="n"/>
-      <c r="X2" s="8" t="inlineStr">
-        <is>
-          <t>FALLO: no se encontró el botón '+ Añadir'</t>
+      <c r="X2" s="9" t="inlineStr">
+        <is>
+          <t>OK (CRUD/Create)</t>
         </is>
       </c>
     </row>
@@ -735,9 +735,9 @@
       <c r="U3" s="2" t="n"/>
       <c r="V3" s="2" t="n"/>
       <c r="W3" s="2" t="n"/>
-      <c r="X3" s="8" t="inlineStr">
-        <is>
-          <t>NO ENCONTRADO (Código=X)</t>
+      <c r="X3" s="9" t="inlineStr">
+        <is>
+          <t>ENCONTRADO: 1 fila(s) (Código=X) → codigo=X | idioma=es-CL | descripcion=CREA QA AUT May 26</t>
         </is>
       </c>
     </row>
@@ -780,9 +780,9 @@
       <c r="U4" s="2" t="n"/>
       <c r="V4" s="2" t="n"/>
       <c r="W4" s="2" t="n"/>
-      <c r="X4" s="9" t="inlineStr">
-        <is>
-          <t>OK (CRUD/Create)</t>
+      <c r="X4" s="8" t="inlineStr">
+        <is>
+          <t>ERROR: Despliegue BCI</t>
         </is>
       </c>
     </row>

--- a/e2e-automationFaseIII/Vaciados/casos_prueba.xlsx
+++ b/e2e-automationFaseIII/Vaciados/casos_prueba.xlsx
@@ -782,7 +782,7 @@
       <c r="W4" s="2" t="n"/>
       <c r="X4" s="8" t="inlineStr">
         <is>
-          <t>ERROR: Despliegue BCI</t>
+          <t>ERROR app: Errores: Error al enviar datos de un maestro</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       <c r="W5" s="2" t="n"/>
       <c r="X5" s="9" t="inlineStr">
         <is>
-          <t>ENCONTRADO: 1 fila(s) (Nombre=Nombre Tarif QA) → codigo=807 | nombre=Nombre Tarif QA</t>
+          <t>ENCONTRADO: 1 fila(s) (Nombre=Nombre Tarif QA) → codigo=808 | nombre=Nombre Tarif QA</t>
         </is>
       </c>
     </row>
